--- a/CE国試data/CE_questions_2016.xlsx
+++ b/CE国試data/CE_questions_2016.xlsx
@@ -2378,7 +2378,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
